--- a/public/exports-from-60-with-coowners/29189420.xlsx
+++ b/public/exports-from-60-with-coowners/29189420.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -25114,12 +25114,12 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018566</t>
+          <t xml:space="preserve">310018578</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -27739,12 +27739,12 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020300</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -27814,12 +27814,12 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020312</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -28339,7 +28339,7 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -28489,7 +28489,7 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -28564,7 +28564,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -29614,7 +29614,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -29764,12 +29764,12 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020327</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -29839,12 +29839,12 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020292</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -30514,7 +30514,7 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -30589,7 +30589,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -34264,12 +34264,12 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -34339,12 +34339,12 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -34414,12 +34414,12 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -34489,12 +34489,12 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -34564,12 +34564,12 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -34639,12 +34639,12 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -34714,12 +34714,12 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -34789,12 +34789,12 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -34864,12 +34864,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -34939,12 +34939,12 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -35014,12 +35014,12 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -35089,12 +35089,12 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -35164,12 +35164,12 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -35239,12 +35239,12 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -35314,12 +35314,12 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -35389,12 +35389,12 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -35464,12 +35464,12 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -35539,12 +35539,12 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -35614,12 +35614,12 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -35689,12 +35689,12 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -35764,12 +35764,12 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -35839,12 +35839,12 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -35914,12 +35914,12 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M480" t="inlineStr">
@@ -36064,12 +36064,12 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -48814,7 +48814,7 @@
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477935</t>
+          <t xml:space="preserve">311477990</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -59314,7 +59314,7 @@
       </c>
       <c r="K791" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555497</t>
+          <t xml:space="preserve">311555498</t>
         </is>
       </c>
       <c r="L791" t="inlineStr">
@@ -63289,7 +63289,7 @@
       </c>
       <c r="K844" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568868</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L844" t="inlineStr">
@@ -63664,7 +63664,7 @@
       </c>
       <c r="K849" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568866</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L849" t="inlineStr">
@@ -69514,12 +69514,12 @@
       </c>
       <c r="K927" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803905</t>
+          <t xml:space="preserve">311803934</t>
         </is>
       </c>
       <c r="L927" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M927" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189420.xlsx
+++ b/public/exports-from-60-with-coowners/29189420.xlsx
@@ -25414,12 +25414,12 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018603</t>
+          <t xml:space="preserve">310018611</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -34264,12 +34264,12 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -34339,12 +34339,12 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -34414,12 +34414,12 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -34489,12 +34489,12 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -34564,12 +34564,12 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -34639,12 +34639,12 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -34714,12 +34714,12 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -34789,12 +34789,12 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -34864,12 +34864,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -34939,12 +34939,12 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -35014,12 +35014,12 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -35089,12 +35089,12 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -35164,12 +35164,12 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -35239,12 +35239,12 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -35314,12 +35314,12 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -35389,12 +35389,12 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -35464,12 +35464,12 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -35539,12 +35539,12 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -35614,12 +35614,12 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -35689,12 +35689,12 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -35764,12 +35764,12 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -35839,12 +35839,12 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -35914,12 +35914,12 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
@@ -36064,12 +36064,12 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -48814,7 +48814,7 @@
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477990</t>
+          <t xml:space="preserve">311477935</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -59314,7 +59314,7 @@
       </c>
       <c r="K791" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555498</t>
+          <t xml:space="preserve">311555497</t>
         </is>
       </c>
       <c r="L791" t="inlineStr">
@@ -63064,7 +63064,7 @@
       </c>
       <c r="K841" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568269</t>
+          <t xml:space="preserve">311568275</t>
         </is>
       </c>
       <c r="L841" t="inlineStr">
@@ -63739,7 +63739,7 @@
       </c>
       <c r="K850" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568867</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L850" t="inlineStr">
@@ -69514,12 +69514,12 @@
       </c>
       <c r="K927" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803934</t>
+          <t xml:space="preserve">311803905</t>
         </is>
       </c>
       <c r="L927" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M927" t="inlineStr">
